--- a/tools/xlsform_samples/EWS.xlsx
+++ b/tools/xlsform_samples/EWS.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1102,84 +1102,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EWS_scoring</t>
+          <t>EWS_environmental_worry</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Computed Scores</t>
+          <t>environmental_worry (mean_coded) - Mean of the administered language variant's items (reverse items recoded).</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>(${ews_en1} + ${ews_en2} + (5 - ${ews_en3}) + ${ews_en4} + (5 - ${ews_en5}) + ${ews_en6} + (5 - ${ews_en7}) + ${ews_en8} + ${ews_en9} + ${ews_en10} + (5 - ${ews_en11}) + (5 - ${ews_en12}) + (5 - ${ews_en13}) + ${ews_en14} + (5 - ${ews_en15}) + (5 - ${ews_en16}) + (5 - ${ews_en17})) div 17</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>EWS_environmental_worry</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>environmental_worry (mean_coded) - Mean of the administered language variant's items (reverse items recoded).</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>(${ews_en1} + ${ews_en2} + (5 - ${ews_en3}) + ${ews_en4} + (5 - ${ews_en5}) + ${ews_en6} + (5 - ${ews_en7}) + ${ews_en8} + ${ews_en9} + ${ews_en10} + (5 - ${ews_en11}) + (5 - ${ews_en12}) + (5 - ${ews_en13}) + ${ews_en14} + (5 - ${ews_en15}) + (5 - ${ews_en16}) + (5 - ${ews_en17}) + ${ews_de1} + ${ews_de2} + ${ews_de3} + ${ews_de4} + ${ews_de5} + ${ews_de6} + ${ews_de7} + ${ews_de8} + ${ews_de9} + ${ews_de10} + ${ews_de11} + ${ews_de12} + ${ews_de13} + ${ews_de14} + ${ews_de15} + ${ews_de16}) div 33</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>EWS_scoring</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/xlsform_samples/EWS.xlsx
+++ b/tools/xlsform_samples/EWS.xlsx
@@ -1291,7 +1291,11 @@
           <t>20260618</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>English (en)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
